--- a/XRD_Results/CuS A1_CuS_XRD_Analysis.xlsx
+++ b/XRD_Results/CuS A1_CuS_XRD_Analysis.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,7 @@
         <v>550.7619999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>175.860228438229</v>
+        <v>163.5499020979016</v>
       </c>
       <c r="F2" t="n">
         <v>35.27088990214662</v>
@@ -480,19 +480,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>20.334</v>
+        <v>17.223</v>
       </c>
       <c r="C3" t="n">
-        <v>4.36393</v>
+        <v>5.14435</v>
       </c>
       <c r="D3" t="n">
-        <v>818.143</v>
+        <v>440.81</v>
       </c>
       <c r="E3" t="n">
-        <v>379.2587459207469</v>
+        <v>52.82973426573415</v>
       </c>
       <c r="F3" t="n">
-        <v>52.39401352528306</v>
+        <v>28.22954557098212</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>22.687</v>
+        <v>20.068</v>
       </c>
       <c r="C4" t="n">
-        <v>3.91632</v>
+        <v>4.42117</v>
       </c>
       <c r="D4" t="n">
-        <v>540.524</v>
+        <v>598.8099999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>102.880652680653</v>
+        <v>75.51538461538451</v>
       </c>
       <c r="F4" t="n">
-        <v>34.6152466827194</v>
+        <v>38.34789179773554</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +520,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>29.153</v>
+        <v>20.334</v>
       </c>
       <c r="C5" t="n">
-        <v>3.06072</v>
+        <v>4.36393</v>
       </c>
       <c r="D5" t="n">
-        <v>1561.52</v>
+        <v>818.143</v>
       </c>
       <c r="E5" t="n">
-        <v>1133.530610722614</v>
+        <v>362.8395664335653</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>52.39401352528306</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +540,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>31.731</v>
+        <v>22.687</v>
       </c>
       <c r="C6" t="n">
-        <v>2.81766</v>
+        <v>3.91632</v>
       </c>
       <c r="D6" t="n">
-        <v>1231.9</v>
+        <v>540.524</v>
       </c>
       <c r="E6" t="n">
-        <v>569.701990675992</v>
+        <v>100.1291818181816</v>
       </c>
       <c r="F6" t="n">
-        <v>78.89108048568062</v>
+        <v>34.6152466827194</v>
       </c>
     </row>
     <row r="7">
@@ -560,19 +560,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>38.73</v>
+        <v>27.659</v>
       </c>
       <c r="C7" t="n">
-        <v>2.32311</v>
+        <v>3.22253</v>
       </c>
       <c r="D7" t="n">
-        <v>675.429</v>
+        <v>772.333</v>
       </c>
       <c r="E7" t="n">
-        <v>126.1514755244759</v>
+        <v>64.51035664335654</v>
       </c>
       <c r="F7" t="n">
-        <v>43.25458527588503</v>
+        <v>49.46033352118449</v>
       </c>
     </row>
     <row r="8">
@@ -580,19 +580,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>47.876</v>
+        <v>29.153</v>
       </c>
       <c r="C8" t="n">
-        <v>1.89846</v>
+        <v>3.06072</v>
       </c>
       <c r="D8" t="n">
-        <v>1371.14</v>
+        <v>1561.52</v>
       </c>
       <c r="E8" t="n">
-        <v>852.1450722610748</v>
+        <v>1116.061006993004</v>
       </c>
       <c r="F8" t="n">
-        <v>87.80803319842205</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
@@ -600,19 +600,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>52.521</v>
+        <v>29.665</v>
       </c>
       <c r="C9" t="n">
-        <v>1.74097</v>
+        <v>3.00909</v>
       </c>
       <c r="D9" t="n">
-        <v>726.7140000000001</v>
+        <v>997.524</v>
       </c>
       <c r="E9" t="n">
-        <v>165.6032960372964</v>
+        <v>61.45081118881103</v>
       </c>
       <c r="F9" t="n">
-        <v>46.53888518879042</v>
+        <v>63.88160254111379</v>
       </c>
     </row>
     <row r="10">
@@ -620,19 +620,199 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>59.172</v>
+        <v>31.711</v>
       </c>
       <c r="C10" t="n">
-        <v>1.56017</v>
+        <v>2.81943</v>
       </c>
       <c r="D10" t="n">
-        <v>821.905</v>
+        <v>1217.81</v>
       </c>
       <c r="E10" t="n">
-        <v>277.5576107226115</v>
+        <v>567.2080279720262</v>
       </c>
       <c r="F10" t="n">
-        <v>52.63493262974538</v>
+        <v>77.98875454685178</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>33.553</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.66877</v>
+      </c>
+      <c r="D11" t="n">
+        <v>791.143</v>
+      </c>
+      <c r="E11" t="n">
+        <v>67.3209160839159</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50.66492904349609</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>38.709</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.32429</v>
+      </c>
+      <c r="D12" t="n">
+        <v>664.143</v>
+      </c>
+      <c r="E12" t="n">
+        <v>121.6173076923073</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.53182796249808</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.20161</v>
+      </c>
+      <c r="D13" t="n">
+        <v>586.7619999999999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53.26664335664316</v>
+      </c>
+      <c r="F13" t="n">
+        <v>37.57633587786259</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>41.553</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2.17153</v>
+      </c>
+      <c r="D14" t="n">
+        <v>561.7140000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>51.5742027972027</v>
+      </c>
+      <c r="F14" t="n">
+        <v>35.97225780009222</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>47.876</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.89846</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1371.14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>852.6671468531445</v>
+      </c>
+      <c r="F15" t="n">
+        <v>87.80803319842205</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>52.521</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.74097</v>
+      </c>
+      <c r="D16" t="n">
+        <v>726.7140000000001</v>
+      </c>
+      <c r="E16" t="n">
+        <v>164.2154265734262</v>
+      </c>
+      <c r="F16" t="n">
+        <v>46.53888518879042</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>59.151</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.56066</v>
+      </c>
+      <c r="D17" t="n">
+        <v>811.1900000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>270.0890419580412</v>
+      </c>
+      <c r="F17" t="n">
+        <v>51.94874225113993</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>62.691</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.48078</v>
+      </c>
+      <c r="D18" t="n">
+        <v>550.2380000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>52.17483916083904</v>
+      </c>
+      <c r="F18" t="n">
+        <v>35.23733285516676</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.42838</v>
+      </c>
+      <c r="D19" t="n">
+        <v>507.857</v>
+      </c>
+      <c r="E19" t="n">
+        <v>53.11447552447544</v>
+      </c>
+      <c r="F19" t="n">
+        <v>32.52324658025514</v>
       </c>
     </row>
   </sheetData>
@@ -20746,7 +20926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:R48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20835,6 +21015,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Phase_Priority</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -20900,10 +21085,13 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
         <v>22.687</v>
@@ -20965,10 +21153,13 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
         <v>22.687</v>
@@ -21030,28 +21221,31 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>29.153</v>
+        <v>27.659</v>
       </c>
       <c r="C5" t="n">
-        <v>3.06072</v>
+        <v>3.22253</v>
       </c>
       <c r="D5" t="n">
-        <v>1561.52</v>
+        <v>772.333</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>49.46033352118449</v>
       </c>
       <c r="F5" t="n">
-        <v>29.1003</v>
+        <v>27.6544</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0661</v>
+        <v>3.223</v>
       </c>
       <c r="H5" t="n">
         <v>5</v>
@@ -21060,31 +21254,31 @@
         <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05269999999999797</v>
+        <v>0.004599999999999937</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0 5 1</t>
+          <t>6 0 3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -21095,41 +21289,44 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>29.153</v>
+        <v>27.659</v>
       </c>
       <c r="C6" t="n">
-        <v>3.06072</v>
+        <v>3.22253</v>
       </c>
       <c r="D6" t="n">
-        <v>1561.52</v>
+        <v>772.333</v>
       </c>
       <c r="E6" t="n">
-        <v>100</v>
+        <v>49.46033352118449</v>
       </c>
       <c r="F6" t="n">
-        <v>29.1003</v>
+        <v>27.8408</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0661</v>
+        <v>3.2018</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05269999999999797</v>
+        <v>0.1818000000000026</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2 5 0</t>
+          <t>-3 3 3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -21160,41 +21357,44 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>29.153</v>
+        <v>27.659</v>
       </c>
       <c r="C7" t="n">
-        <v>3.06072</v>
+        <v>3.22253</v>
       </c>
       <c r="D7" t="n">
-        <v>1561.52</v>
+        <v>772.333</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>49.46033352118449</v>
       </c>
       <c r="F7" t="n">
-        <v>29.2781</v>
+        <v>27.8408</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0478</v>
+        <v>3.2018</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1250999999999998</v>
+        <v>0.1818000000000026</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 3 3</t>
+          <t>3 3 3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -21225,61 +21425,64 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.153</v>
+        <v>27.659</v>
       </c>
       <c r="C8" t="n">
-        <v>3.06072</v>
+        <v>3.22253</v>
       </c>
       <c r="D8" t="n">
-        <v>1561.52</v>
+        <v>772.333</v>
       </c>
       <c r="E8" t="n">
-        <v>100</v>
+        <v>49.46033352118449</v>
       </c>
       <c r="F8" t="n">
-        <v>29.2781</v>
+        <v>27.8619</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0478</v>
+        <v>3.1995</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>261</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>26.12612612612612</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1250999999999998</v>
+        <v>0.2028999999999996</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-1 5 1</t>
+          <t>1 0 1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -21290,10 +21493,13 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
         <v>29.153</v>
@@ -21308,57 +21514,60 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>29.0043</v>
+        <v>29.1003</v>
       </c>
       <c r="G9" t="n">
-        <v>3.076</v>
+        <v>3.0661</v>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1486999999999981</v>
+        <v>0.05269999999999797</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6 0 5</t>
+          <t>0 5 1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
         <v>29.153</v>
@@ -21373,23 +21582,23 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>29.3679</v>
+        <v>29.1003</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0387</v>
+        <v>3.0661</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2149000000000001</v>
+        <v>0.05269999999999797</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-4 4 2</t>
+          <t>2 5 0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -21413,17 +21622,20 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
         <v>29.153</v>
@@ -21438,23 +21650,23 @@
         <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>29.3679</v>
+        <v>29.2781</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0387</v>
+        <v>3.0478</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2149000000000001</v>
+        <v>0.1250999999999998</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 4 2</t>
+          <t>4 3 3</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -21478,35 +21690,38 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B12" t="n">
-        <v>31.731</v>
+        <v>29.153</v>
       </c>
       <c r="C12" t="n">
-        <v>2.81766</v>
+        <v>3.06072</v>
       </c>
       <c r="D12" t="n">
-        <v>1231.9</v>
+        <v>1561.52</v>
       </c>
       <c r="E12" t="n">
-        <v>78.89108048568062</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>31.7366</v>
+        <v>29.2781</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8171</v>
+        <v>3.0478</v>
       </c>
       <c r="H12" t="n">
         <v>17</v>
@@ -21515,11 +21730,11 @@
         <v>17</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005599999999997607</v>
+        <v>0.1250999999999998</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-3 4 3</t>
+          <t>-1 5 1</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -21543,113 +21758,119 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" t="n">
+        <v>29.153</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.06072</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1561.52</v>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" t="n">
+        <v>29.0043</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.076</v>
+      </c>
+      <c r="H13" t="n">
+        <v>85</v>
+      </c>
+      <c r="I13" t="n">
+        <v>85</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1486999999999981</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6 0 5</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="n">
-        <v>31.731</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2.81766</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1231.9</v>
-      </c>
-      <c r="E13" t="n">
-        <v>78.89108048568062</v>
-      </c>
-      <c r="F13" t="n">
-        <v>31.7366</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2.8171</v>
-      </c>
-      <c r="H13" t="n">
-        <v>17</v>
-      </c>
-      <c r="I13" t="n">
-        <v>17</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.005599999999997607</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>3 4 3</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>2</v>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>31.731</v>
+        <v>29.153</v>
       </c>
       <c r="C14" t="n">
-        <v>2.81766</v>
+        <v>3.06072</v>
       </c>
       <c r="D14" t="n">
-        <v>1231.9</v>
+        <v>1561.52</v>
       </c>
       <c r="E14" t="n">
-        <v>78.89108048568062</v>
+        <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>31.6072</v>
+        <v>29.3679</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8284</v>
+        <v>3.0387</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1238000000000028</v>
+        <v>0.2149000000000001</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1 3 4</t>
+          <t>-4 4 2</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -21673,48 +21894,51 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B15" t="n">
-        <v>31.731</v>
+        <v>29.153</v>
       </c>
       <c r="C15" t="n">
-        <v>2.81766</v>
+        <v>3.06072</v>
       </c>
       <c r="D15" t="n">
-        <v>1231.9</v>
+        <v>1561.52</v>
       </c>
       <c r="E15" t="n">
-        <v>78.89108048568062</v>
+        <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>31.6072</v>
+        <v>29.3679</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8284</v>
+        <v>3.0387</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1238000000000028</v>
+        <v>0.2149000000000001</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-4 2 4</t>
+          <t>4 4 2</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -21738,113 +21962,119 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
         <v>4</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B16" t="n">
-        <v>31.731</v>
+        <v>29.665</v>
       </c>
       <c r="C16" t="n">
-        <v>2.81766</v>
+        <v>3.00909</v>
       </c>
       <c r="D16" t="n">
-        <v>1231.9</v>
+        <v>997.524</v>
       </c>
       <c r="E16" t="n">
-        <v>78.89108048568062</v>
+        <v>63.88160254111379</v>
       </c>
       <c r="F16" t="n">
-        <v>31.982</v>
+        <v>29.6586</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7961</v>
+        <v>3.0096</v>
       </c>
       <c r="H16" t="n">
-        <v>999</v>
+        <v>21</v>
       </c>
       <c r="I16" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2509999999999977</v>
+        <v>0.006399999999999295</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1 0 3</t>
+          <t>8 0 2</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B17" t="n">
-        <v>31.731</v>
+        <v>29.665</v>
       </c>
       <c r="C17" t="n">
-        <v>2.81766</v>
+        <v>3.00909</v>
       </c>
       <c r="D17" t="n">
-        <v>1231.9</v>
+        <v>997.524</v>
       </c>
       <c r="E17" t="n">
-        <v>78.89108048568062</v>
+        <v>63.88160254111379</v>
       </c>
       <c r="F17" t="n">
-        <v>31.4753</v>
+        <v>29.5944</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8399</v>
+        <v>3.016</v>
       </c>
       <c r="H17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2557000000000009</v>
+        <v>0.07059999999999889</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-1 5 2</t>
+          <t>-8 2 1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -21868,48 +22098,51 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B18" t="n">
-        <v>31.731</v>
+        <v>29.665</v>
       </c>
       <c r="C18" t="n">
-        <v>2.81766</v>
+        <v>3.00909</v>
       </c>
       <c r="D18" t="n">
-        <v>1231.9</v>
+        <v>997.524</v>
       </c>
       <c r="E18" t="n">
-        <v>78.89108048568062</v>
+        <v>63.88160254111379</v>
       </c>
       <c r="F18" t="n">
-        <v>31.4753</v>
+        <v>29.5944</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8399</v>
+        <v>3.016</v>
       </c>
       <c r="H18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2557000000000009</v>
+        <v>0.07059999999999889</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1 5 2</t>
+          <t>-8 0 2</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -21933,48 +22166,51 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B19" t="n">
-        <v>38.73</v>
+        <v>29.665</v>
       </c>
       <c r="C19" t="n">
-        <v>2.32311</v>
+        <v>3.00909</v>
       </c>
       <c r="D19" t="n">
-        <v>675.429</v>
+        <v>997.524</v>
       </c>
       <c r="E19" t="n">
-        <v>43.25458527588503</v>
+        <v>63.88160254111379</v>
       </c>
       <c r="F19" t="n">
-        <v>38.7261</v>
+        <v>29.8547</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3233</v>
+        <v>2.9903</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.003899999999994463</v>
+        <v>0.189700000000002</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-5 6 1</t>
+          <t>-2 5 1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -21998,48 +22234,51 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B20" t="n">
-        <v>38.73</v>
+        <v>29.665</v>
       </c>
       <c r="C20" t="n">
-        <v>2.32311</v>
+        <v>3.00909</v>
       </c>
       <c r="D20" t="n">
-        <v>675.429</v>
+        <v>997.524</v>
       </c>
       <c r="E20" t="n">
-        <v>43.25458527588503</v>
+        <v>63.88160254111379</v>
       </c>
       <c r="F20" t="n">
-        <v>38.7261</v>
+        <v>29.8547</v>
       </c>
       <c r="G20" t="n">
-        <v>2.3233</v>
+        <v>2.9903</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.003899999999994463</v>
+        <v>0.189700000000002</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>5 6 1</t>
+          <t>2 5 1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -22063,113 +22302,119 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" t="n">
+        <v>29.665</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.00909</v>
+      </c>
+      <c r="D21" t="n">
+        <v>997.524</v>
+      </c>
+      <c r="E21" t="n">
+        <v>63.88160254111379</v>
+      </c>
+      <c r="F21" t="n">
+        <v>29.4683</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.0286</v>
+      </c>
+      <c r="H21" t="n">
+        <v>572</v>
+      </c>
+      <c r="I21" t="n">
+        <v>57.25725725725725</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1966999999999999</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>1 0 2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
         <v>6</v>
       </c>
-      <c r="B21" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D21" t="n">
-        <v>675.429</v>
-      </c>
-      <c r="E21" t="n">
-        <v>43.25458527588503</v>
-      </c>
-      <c r="F21" t="n">
-        <v>38.642</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.3281</v>
-      </c>
-      <c r="H21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.08799999999999386</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>-3 3 5</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>3</v>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B22" t="n">
-        <v>38.73</v>
+        <v>29.665</v>
       </c>
       <c r="C22" t="n">
-        <v>2.32311</v>
+        <v>3.00909</v>
       </c>
       <c r="D22" t="n">
-        <v>675.429</v>
+        <v>997.524</v>
       </c>
       <c r="E22" t="n">
-        <v>43.25458527588503</v>
+        <v>63.88160254111379</v>
       </c>
       <c r="F22" t="n">
-        <v>38.642</v>
+        <v>29.3679</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3281</v>
+        <v>3.0387</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08799999999999386</v>
+        <v>0.2971000000000004</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>5 5 3</t>
+          <t>-4 4 2</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -22193,48 +22438,51 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
         <v>4</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B23" t="n">
-        <v>38.73</v>
+        <v>29.665</v>
       </c>
       <c r="C23" t="n">
-        <v>2.32311</v>
+        <v>3.00909</v>
       </c>
       <c r="D23" t="n">
-        <v>675.429</v>
+        <v>997.524</v>
       </c>
       <c r="E23" t="n">
-        <v>43.25458527588503</v>
+        <v>63.88160254111379</v>
       </c>
       <c r="F23" t="n">
-        <v>38.8318</v>
+        <v>29.3679</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3172</v>
+        <v>3.0387</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1018000000000043</v>
+        <v>0.2971000000000004</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-5 2 5</t>
+          <t>4 4 2</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -22258,48 +22506,51 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B24" t="n">
-        <v>38.73</v>
+        <v>31.711</v>
       </c>
       <c r="C24" t="n">
-        <v>2.32311</v>
+        <v>2.81943</v>
       </c>
       <c r="D24" t="n">
-        <v>675.429</v>
+        <v>1217.81</v>
       </c>
       <c r="E24" t="n">
-        <v>43.25458527588503</v>
+        <v>77.98875454685178</v>
       </c>
       <c r="F24" t="n">
-        <v>38.8318</v>
+        <v>31.7366</v>
       </c>
       <c r="G24" t="n">
-        <v>2.3172</v>
+        <v>2.8171</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1018000000000043</v>
+        <v>0.02560000000000073</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>5 4 4</t>
+          <t>-3 4 3</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -22323,48 +22574,51 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>38.73</v>
+        <v>31.711</v>
       </c>
       <c r="C25" t="n">
-        <v>2.32311</v>
+        <v>2.81943</v>
       </c>
       <c r="D25" t="n">
-        <v>675.429</v>
+        <v>1217.81</v>
       </c>
       <c r="E25" t="n">
-        <v>43.25458527588503</v>
+        <v>77.98875454685178</v>
       </c>
       <c r="F25" t="n">
-        <v>38.5213</v>
+        <v>31.7366</v>
       </c>
       <c r="G25" t="n">
-        <v>2.3351</v>
+        <v>2.8171</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2087000000000003</v>
+        <v>0.02560000000000073</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11 2 0</t>
+          <t>3 4 3</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -22388,203 +22642,219 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B26" t="n">
-        <v>47.876</v>
+        <v>31.711</v>
       </c>
       <c r="C26" t="n">
-        <v>1.89846</v>
+        <v>2.81943</v>
       </c>
       <c r="D26" t="n">
-        <v>1371.14</v>
+        <v>1217.81</v>
       </c>
       <c r="E26" t="n">
-        <v>87.80803319842205</v>
+        <v>77.98875454685178</v>
       </c>
       <c r="F26" t="n">
-        <v>48.0177</v>
+        <v>31.6072</v>
       </c>
       <c r="G26" t="n">
-        <v>1.8931</v>
+        <v>2.8284</v>
       </c>
       <c r="H26" t="n">
-        <v>165</v>
+        <v>14</v>
       </c>
       <c r="I26" t="n">
-        <v>16.51651651651652</v>
+        <v>14</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1417000000000002</v>
+        <v>0.1037999999999997</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1 0 7</t>
+          <t>1 3 4</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" t="n">
-        <v>52.521</v>
+        <v>31.711</v>
       </c>
       <c r="C27" t="n">
-        <v>1.74097</v>
+        <v>2.81943</v>
       </c>
       <c r="D27" t="n">
-        <v>726.7140000000001</v>
+        <v>1217.81</v>
       </c>
       <c r="E27" t="n">
-        <v>46.53888518879042</v>
+        <v>77.98875454685178</v>
       </c>
       <c r="F27" t="n">
-        <v>52.4649</v>
+        <v>31.6072</v>
       </c>
       <c r="G27" t="n">
-        <v>1.7427</v>
+        <v>2.8284</v>
       </c>
       <c r="H27" t="n">
-        <v>519</v>
+        <v>14</v>
       </c>
       <c r="I27" t="n">
-        <v>51.95195195195195</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0561000000000007</v>
+        <v>0.1037999999999997</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2 2 0</t>
+          <t>-4 2 4</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>CuCl</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>000822117</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" t="n">
-        <v>52.521</v>
+        <v>31.711</v>
       </c>
       <c r="C28" t="n">
-        <v>1.74097</v>
+        <v>2.81943</v>
       </c>
       <c r="D28" t="n">
-        <v>726.7140000000001</v>
+        <v>1217.81</v>
       </c>
       <c r="E28" t="n">
-        <v>46.53888518879042</v>
+        <v>77.98875454685178</v>
       </c>
       <c r="F28" t="n">
-        <v>52.6163</v>
+        <v>31.4753</v>
       </c>
       <c r="G28" t="n">
-        <v>1.738</v>
+        <v>2.8399</v>
       </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I28" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>0.09530000000000172</v>
+        <v>0.2356999999999978</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6 6 10</t>
+          <t>-1 5 2</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -22592,64 +22862,1351 @@
         <v>9</v>
       </c>
       <c r="B29" t="n">
-        <v>59.172</v>
+        <v>31.711</v>
       </c>
       <c r="C29" t="n">
-        <v>1.56017</v>
+        <v>2.81943</v>
       </c>
       <c r="D29" t="n">
-        <v>821.905</v>
+        <v>1217.81</v>
       </c>
       <c r="E29" t="n">
-        <v>52.63493262974538</v>
+        <v>77.98875454685178</v>
       </c>
       <c r="F29" t="n">
+        <v>31.4753</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.8399</v>
+      </c>
+      <c r="H29" t="n">
+        <v>21</v>
+      </c>
+      <c r="I29" t="n">
+        <v>21</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.2356999999999978</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>1 5 2</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" t="n">
+        <v>31.711</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.81943</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1217.81</v>
+      </c>
+      <c r="E30" t="n">
+        <v>77.98875454685178</v>
+      </c>
+      <c r="F30" t="n">
+        <v>31.982</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.7961</v>
+      </c>
+      <c r="H30" t="n">
+        <v>999</v>
+      </c>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.2710000000000008</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1 0 3</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" t="n">
+        <v>33.553</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.66877</v>
+      </c>
+      <c r="D31" t="n">
+        <v>791.143</v>
+      </c>
+      <c r="E31" t="n">
+        <v>50.66492904349609</v>
+      </c>
+      <c r="F31" t="n">
+        <v>33.6668</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.6599</v>
+      </c>
+      <c r="H31" t="n">
+        <v>26</v>
+      </c>
+      <c r="I31" t="n">
+        <v>26</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.1138000000000048</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>5 5 1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" t="n">
+        <v>33.553</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.66877</v>
+      </c>
+      <c r="D32" t="n">
+        <v>791.143</v>
+      </c>
+      <c r="E32" t="n">
+        <v>50.66492904349609</v>
+      </c>
+      <c r="F32" t="n">
+        <v>33.6668</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.6599</v>
+      </c>
+      <c r="H32" t="n">
+        <v>26</v>
+      </c>
+      <c r="I32" t="n">
+        <v>26</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.1138000000000048</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>1 1 5</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" t="n">
+        <v>33.553</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.66877</v>
+      </c>
+      <c r="D33" t="n">
+        <v>791.143</v>
+      </c>
+      <c r="E33" t="n">
+        <v>50.66492904349609</v>
+      </c>
+      <c r="F33" t="n">
+        <v>33.283</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.6897</v>
+      </c>
+      <c r="H33" t="n">
+        <v>11</v>
+      </c>
+      <c r="I33" t="n">
+        <v>11</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.269999999999996</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>5 2 4</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" t="n">
+        <v>33.553</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.66877</v>
+      </c>
+      <c r="D34" t="n">
+        <v>791.143</v>
+      </c>
+      <c r="E34" t="n">
+        <v>50.66492904349609</v>
+      </c>
+      <c r="F34" t="n">
+        <v>33.283</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.6897</v>
+      </c>
+      <c r="H34" t="n">
+        <v>11</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.269999999999996</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>10 0 0</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B35" t="n">
+        <v>38.709</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2.32429</v>
+      </c>
+      <c r="D35" t="n">
+        <v>664.143</v>
+      </c>
+      <c r="E35" t="n">
+        <v>42.53182796249808</v>
+      </c>
+      <c r="F35" t="n">
+        <v>38.7261</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.3233</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.01709999999999923</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>-5 6 1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>11</v>
+      </c>
+      <c r="B36" t="n">
+        <v>38.709</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.32429</v>
+      </c>
+      <c r="D36" t="n">
+        <v>664.143</v>
+      </c>
+      <c r="E36" t="n">
+        <v>42.53182796249808</v>
+      </c>
+      <c r="F36" t="n">
+        <v>38.7261</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.3233</v>
+      </c>
+      <c r="H36" t="n">
+        <v>8</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.01709999999999923</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>5 6 1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>11</v>
+      </c>
+      <c r="B37" t="n">
+        <v>38.709</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.32429</v>
+      </c>
+      <c r="D37" t="n">
+        <v>664.143</v>
+      </c>
+      <c r="E37" t="n">
+        <v>42.53182796249808</v>
+      </c>
+      <c r="F37" t="n">
+        <v>38.642</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.3281</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.06700000000000017</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>-3 3 5</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" t="n">
+        <v>38.709</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.32429</v>
+      </c>
+      <c r="D38" t="n">
+        <v>664.143</v>
+      </c>
+      <c r="E38" t="n">
+        <v>42.53182796249808</v>
+      </c>
+      <c r="F38" t="n">
+        <v>38.642</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.3281</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.06700000000000017</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5 5 3</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" t="n">
+        <v>38.709</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.32429</v>
+      </c>
+      <c r="D39" t="n">
+        <v>664.143</v>
+      </c>
+      <c r="E39" t="n">
+        <v>42.53182796249808</v>
+      </c>
+      <c r="F39" t="n">
+        <v>38.8318</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.122799999999998</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>-5 2 5</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>11</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38.709</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.32429</v>
+      </c>
+      <c r="D40" t="n">
+        <v>664.143</v>
+      </c>
+      <c r="E40" t="n">
+        <v>42.53182796249808</v>
+      </c>
+      <c r="F40" t="n">
+        <v>38.8318</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.122799999999998</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5 4 4</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B41" t="n">
+        <v>38.709</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.32429</v>
+      </c>
+      <c r="D41" t="n">
+        <v>664.143</v>
+      </c>
+      <c r="E41" t="n">
+        <v>42.53182796249808</v>
+      </c>
+      <c r="F41" t="n">
+        <v>38.5213</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.3351</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.1877000000000066</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>11 2 0</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>13</v>
+      </c>
+      <c r="B42" t="n">
+        <v>41.553</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.17153</v>
+      </c>
+      <c r="D42" t="n">
+        <v>561.7140000000001</v>
+      </c>
+      <c r="E42" t="n">
+        <v>35.97225780009222</v>
+      </c>
+      <c r="F42" t="n">
+        <v>41.2844</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="H42" t="n">
+        <v>8</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.2685999999999993</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0 0 19</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>14</v>
+      </c>
+      <c r="B43" t="n">
+        <v>47.876</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.89846</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1371.14</v>
+      </c>
+      <c r="E43" t="n">
+        <v>87.80803319842205</v>
+      </c>
+      <c r="F43" t="n">
+        <v>48.0177</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.8931</v>
+      </c>
+      <c r="H43" t="n">
+        <v>165</v>
+      </c>
+      <c r="I43" t="n">
+        <v>16.51651651651652</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.1417000000000002</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1 0 7</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>15</v>
+      </c>
+      <c r="B44" t="n">
+        <v>52.521</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.74097</v>
+      </c>
+      <c r="D44" t="n">
+        <v>726.7140000000001</v>
+      </c>
+      <c r="E44" t="n">
+        <v>46.53888518879042</v>
+      </c>
+      <c r="F44" t="n">
+        <v>52.4649</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.7427</v>
+      </c>
+      <c r="H44" t="n">
+        <v>519</v>
+      </c>
+      <c r="I44" t="n">
+        <v>51.95195195195195</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.0561000000000007</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2 2 0</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>000822117</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>15</v>
+      </c>
+      <c r="B45" t="n">
+        <v>52.521</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.74097</v>
+      </c>
+      <c r="D45" t="n">
+        <v>726.7140000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>46.53888518879042</v>
+      </c>
+      <c r="F45" t="n">
+        <v>52.6163</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.738</v>
+      </c>
+      <c r="H45" t="n">
+        <v>12</v>
+      </c>
+      <c r="I45" t="n">
+        <v>12</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.09530000000000172</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6 6 10</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>16</v>
+      </c>
+      <c r="B46" t="n">
+        <v>59.151</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.56066</v>
+      </c>
+      <c r="D46" t="n">
+        <v>811.1900000000001</v>
+      </c>
+      <c r="E46" t="n">
+        <v>51.94874225113993</v>
+      </c>
+      <c r="F46" t="n">
         <v>59.0765</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G46" t="n">
         <v>1.5624</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H46" t="n">
         <v>104</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I46" t="n">
         <v>10.41041041041041</v>
       </c>
-      <c r="J29" t="n">
-        <v>0.09549999999999415</v>
-      </c>
-      <c r="K29" t="inlineStr">
+      <c r="J46" t="n">
+        <v>0.07450000000000045</v>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>2 0 3</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>CuS</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Covellite</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>CuS</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>000752233</t>
         </is>
       </c>
-      <c r="P29" t="n">
+      <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>18</v>
+      </c>
+      <c r="B47" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.42838</v>
+      </c>
+      <c r="D47" t="n">
+        <v>507.857</v>
+      </c>
+      <c r="E47" t="n">
+        <v>32.52324658025514</v>
+      </c>
+      <c r="F47" t="n">
+        <v>65.4935</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="H47" t="n">
+        <v>8</v>
+      </c>
+      <c r="I47" t="n">
+        <v>8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.2235000000000014</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>12 0 15</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>18</v>
+      </c>
+      <c r="B48" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.42838</v>
+      </c>
+      <c r="D48" t="n">
+        <v>507.857</v>
+      </c>
+      <c r="E48" t="n">
+        <v>32.52324658025514</v>
+      </c>
+      <c r="F48" t="n">
+        <v>65.5515</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.4229</v>
+      </c>
+      <c r="H48" t="n">
+        <v>139</v>
+      </c>
+      <c r="I48" t="n">
+        <v>13.91391391391391</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.2815000000000083</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>2 2 2</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>000822117</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -22663,7 +24220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22752,6 +24309,11 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Phase_Priority</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -22817,10 +24379,13 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
         <v>22.687</v>
@@ -22882,317 +24447,336 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B4" t="n">
+        <v>27.659</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.22253</v>
+      </c>
+      <c r="D4" t="n">
+        <v>772.333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>49.46033352118449</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27.8619</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.1995</v>
+      </c>
+      <c r="H4" t="n">
+        <v>261</v>
+      </c>
+      <c r="I4" t="n">
+        <v>26.12612612612612</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2028999999999996</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1 0 1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>4</v>
       </c>
-      <c r="B4" t="n">
-        <v>29.153</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.06072</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1561.52</v>
-      </c>
-      <c r="E4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>29.1003</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.0661</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.05269999999999797</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0 5 1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
         <v>1</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>29.153</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.06072</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1561.52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>29.0043</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.076</v>
+      </c>
+      <c r="H5" t="n">
+        <v>85</v>
+      </c>
+      <c r="I5" t="n">
+        <v>85</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1486999999999981</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6 0 5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>5</v>
       </c>
-      <c r="B5" t="n">
-        <v>31.731</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2.81766</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1231.9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>78.89108048568062</v>
-      </c>
-      <c r="F5" t="n">
-        <v>31.7366</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.8171</v>
-      </c>
-      <c r="H5" t="n">
-        <v>17</v>
-      </c>
-      <c r="I5" t="n">
-        <v>17</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.005599999999997607</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-3 4 3</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="n">
+        <v>29.665</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.00909</v>
+      </c>
+      <c r="D6" t="n">
+        <v>997.524</v>
+      </c>
+      <c r="E6" t="n">
+        <v>63.88160254111379</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29.4683</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.0286</v>
+      </c>
+      <c r="H6" t="n">
+        <v>572</v>
+      </c>
+      <c r="I6" t="n">
+        <v>57.25725725725725</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1966999999999999</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1 0 2</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>6</v>
       </c>
-      <c r="B6" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D6" t="n">
-        <v>675.429</v>
-      </c>
-      <c r="E6" t="n">
-        <v>43.25458527588503</v>
-      </c>
-      <c r="F6" t="n">
-        <v>38.7261</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.3233</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.003899999999994463</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-5 6 1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
         <v>1</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B7" t="n">
+        <v>31.711</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.81943</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1217.81</v>
+      </c>
+      <c r="E7" t="n">
+        <v>77.98875454685178</v>
+      </c>
+      <c r="F7" t="n">
+        <v>31.982</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.7961</v>
+      </c>
+      <c r="H7" t="n">
+        <v>999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2710000000000008</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1 0 3</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>7</v>
       </c>
-      <c r="B7" t="n">
-        <v>47.876</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.89846</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1371.14</v>
-      </c>
-      <c r="E7" t="n">
-        <v>87.80803319842205</v>
-      </c>
-      <c r="F7" t="n">
-        <v>48.0177</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.8931</v>
-      </c>
-      <c r="H7" t="n">
-        <v>165</v>
-      </c>
-      <c r="I7" t="n">
-        <v>16.51651651651652</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.1417000000000002</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1 0 7</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
         <v>1</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>52.521</v>
+        <v>33.553</v>
       </c>
       <c r="C8" t="n">
-        <v>1.74097</v>
+        <v>2.66877</v>
       </c>
       <c r="D8" t="n">
-        <v>726.7140000000001</v>
+        <v>791.143</v>
       </c>
       <c r="E8" t="n">
-        <v>46.53888518879042</v>
+        <v>50.66492904349609</v>
       </c>
       <c r="F8" t="n">
-        <v>52.4649</v>
+        <v>33.6668</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7427</v>
+        <v>2.6599</v>
       </c>
       <c r="H8" t="n">
-        <v>519</v>
+        <v>26</v>
       </c>
       <c r="I8" t="n">
-        <v>51.95195195195195</v>
+        <v>26</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0561000000000007</v>
+        <v>0.1138000000000048</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2 2 0</t>
+          <t>5 5 1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>CuCl</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>000822117</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -23203,61 +24787,64 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>59.172</v>
+        <v>38.709</v>
       </c>
       <c r="C9" t="n">
-        <v>1.56017</v>
+        <v>2.32429</v>
       </c>
       <c r="D9" t="n">
-        <v>821.905</v>
+        <v>664.143</v>
       </c>
       <c r="E9" t="n">
-        <v>52.63493262974538</v>
+        <v>42.53182796249808</v>
       </c>
       <c r="F9" t="n">
-        <v>59.0765</v>
+        <v>38.7261</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5624</v>
+        <v>2.3233</v>
       </c>
       <c r="H9" t="n">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>10.41041041041041</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09549999999999415</v>
+        <v>0.01709999999999923</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2 0 3</t>
+          <t>-5 6 1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -23267,6 +24854,349 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B10" t="n">
+        <v>41.553</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.17153</v>
+      </c>
+      <c r="D10" t="n">
+        <v>561.7140000000001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>35.97225780009222</v>
+      </c>
+      <c r="F10" t="n">
+        <v>41.2844</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.185</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2685999999999993</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0 0 19</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B11" t="n">
+        <v>47.876</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.89846</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1371.14</v>
+      </c>
+      <c r="E11" t="n">
+        <v>87.80803319842205</v>
+      </c>
+      <c r="F11" t="n">
+        <v>48.0177</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.8931</v>
+      </c>
+      <c r="H11" t="n">
+        <v>165</v>
+      </c>
+      <c r="I11" t="n">
+        <v>16.51651651651652</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1417000000000002</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1 0 7</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15</v>
+      </c>
+      <c r="B12" t="n">
+        <v>52.521</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.74097</v>
+      </c>
+      <c r="D12" t="n">
+        <v>726.7140000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>46.53888518879042</v>
+      </c>
+      <c r="F12" t="n">
+        <v>52.6163</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.738</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.09530000000000172</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6 6 10</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16</v>
+      </c>
+      <c r="B13" t="n">
+        <v>59.151</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.56066</v>
+      </c>
+      <c r="D13" t="n">
+        <v>811.1900000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>51.94874225113993</v>
+      </c>
+      <c r="F13" t="n">
+        <v>59.0765</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.5624</v>
+      </c>
+      <c r="H13" t="n">
+        <v>104</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10.41041041041041</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.07450000000000045</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2 0 3</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B14" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.42838</v>
+      </c>
+      <c r="D14" t="n">
+        <v>507.857</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32.52324658025514</v>
+      </c>
+      <c r="F14" t="n">
+        <v>65.4935</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2235000000000014</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>12 0 15</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -23280,7 +25210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23340,34 +25270,186 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
+        <v>17.223</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.14435</v>
+      </c>
+      <c r="D2" t="n">
+        <v>440.81</v>
+      </c>
+      <c r="E2" t="n">
+        <v>28.22954557098212</v>
+      </c>
+      <c r="F2" t="n">
+        <v>16.6376</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.5853999999999999</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>20.068</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.42117</v>
+      </c>
+      <c r="D3" t="n">
+        <v>598.8099999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>38.34789179773554</v>
+      </c>
+      <c r="F3" t="n">
+        <v>20.6644</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.5963999999999992</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
         <v>20.334</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C4" t="n">
         <v>4.36393</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D4" t="n">
         <v>818.143</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E4" t="n">
         <v>52.39401352528306</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F4" t="n">
         <v>20.6644</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.3304000000000009</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>40.96</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.20161</v>
+      </c>
+      <c r="D5" t="n">
+        <v>586.7619999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37.57633587786259</v>
+      </c>
+      <c r="F5" t="n">
+        <v>41.2844</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3243999999999971</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B6" t="n">
+        <v>62.691</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.48078</v>
+      </c>
+      <c r="D6" t="n">
+        <v>550.2380000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>35.23733285516676</v>
+      </c>
+      <c r="F6" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3673999999999964</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>NO MATCH</t>
         </is>
@@ -23466,111 +25548,111 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02847499999999759</v>
+        <v>0.06415714285714356</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05269999999999797</v>
+        <v>0.1818000000000026</v>
       </c>
       <c r="H2" t="n">
-        <v>256.7609124442851</v>
+        <v>419.1426942978636</v>
       </c>
       <c r="I2" t="n">
-        <v>44.44444444444444</v>
+        <v>38.88888888888889</v>
       </c>
       <c r="J2" t="n">
         <v>116</v>
       </c>
       <c r="K2" t="n">
-        <v>3.448275862068965</v>
+        <v>6.03448275862069</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1627333333333306</v>
+        <v>0.1563500000000003</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2509999999999977</v>
+        <v>0.2685999999999993</v>
       </c>
       <c r="H3" t="n">
-        <v>219.334046313848</v>
+        <v>299.7656129924689</v>
       </c>
       <c r="I3" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K3" t="n">
-        <v>20</v>
+        <v>19.35483870967742</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1471333333333339</v>
+        <v>0.1773600000000002</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1974000000000018</v>
+        <v>0.2710000000000008</v>
       </c>
       <c r="H4" t="n">
-        <v>181.809775090937</v>
+        <v>331.087466058712</v>
       </c>
       <c r="I4" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K4" t="n">
         <v>33.33333333333333</v>
-      </c>
-      <c r="J4" t="n">
-        <v>31</v>
-      </c>
-      <c r="K4" t="n">
-        <v>9.67741935483871</v>
       </c>
     </row>
     <row r="5">
@@ -23591,16 +25673,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0561000000000007</v>
+        <v>0.1688000000000045</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0561000000000007</v>
+        <v>0.2815000000000083</v>
       </c>
       <c r="H5" t="n">
-        <v>46.53888518879042</v>
+        <v>79.06213176904555</v>
       </c>
       <c r="I5" t="n">
         <v>11.11111111111111</v>
@@ -23609,7 +25691,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
